--- a/sc/qa/unit/data/xlsx/pivot-table/PivotTableCellFormatsTest_14_TwoRowsDataFieldInColumn_LabelColor.xlsx
+++ b/sc/qa/unit/data/xlsx/pivot-table/PivotTableCellFormatsTest_14_TwoRowsDataFieldInColumn_LabelColor.xlsx
@@ -1,29 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\VBOXSVR\quikee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F9C63F-8804-41F4-AE3F-23FAE15F580B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{D1F9C63F-8804-41F4-AE3F-23FAE15F580B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD887200-11DB-46D9-B87E-7A68D9BB254D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="16224" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId2"/>
+    <pivotCache cacheId="80" r:id="rId2"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
   <si>
     <t>A</t>
   </si>
@@ -246,14 +262,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -268,72 +284,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45B73C9B-B454-EDAB-0098-DD0095949706}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3611880" y="2560320"/>
-          <a:ext cx="2644140" cy="1836420"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -410,7 +360,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" colGrandTotals="0" createdVersion="8" indent="0" compact="0" outline="1" compactData="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="80" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" colGrandTotals="0" createdVersion="8" indent="0" compact="0" outline="1" compactData="0">
   <location ref="G4:J13" firstHeaderRow="0" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" showAll="0">
@@ -481,7 +431,7 @@
     <dataField name="Sum of D" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -490,7 +440,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -770,19 +720,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.45"/>
   <cols>
-    <col min="7" max="7" width="12.5546875" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="8" max="8" width="8.5" customWidth="1"/>
+    <col min="9" max="9" width="8.75" customWidth="1"/>
+    <col min="10" max="10" width="8.5" customWidth="1"/>
+    <col min="11" max="11" width="8.625" customWidth="1"/>
     <col min="12" max="12" width="4" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
+    <col min="13" max="13" width="6.625" customWidth="1"/>
     <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="6.6640625" customWidth="1"/>
-    <col min="16" max="16" width="10.77734375" customWidth="1"/>
+    <col min="15" max="15" width="6.625" customWidth="1"/>
+    <col min="16" max="16" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -973,8 +923,129 @@
         <v>25</v>
       </c>
     </row>
+    <row r="15" spans="1:10">
+      <c r="G15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="1">
+        <v>3</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10">
+      <c r="G17" s="5"/>
+      <c r="H17" s="7">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>3</v>
+      </c>
+      <c r="J17" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10">
+      <c r="G18" s="5">
+        <v>2</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="5">
+        <v>3</v>
+      </c>
+      <c r="J18" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="7:10">
+      <c r="G19" s="5"/>
+      <c r="H19" s="7">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5">
+        <v>3</v>
+      </c>
+      <c r="J19" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="7:10">
+      <c r="G20" s="5">
+        <v>3</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="5">
+        <v>4</v>
+      </c>
+      <c r="J20" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="7:10">
+      <c r="G21" s="5"/>
+      <c r="H21" s="7">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5">
+        <v>4</v>
+      </c>
+      <c r="J21" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="7:10">
+      <c r="G22" s="5">
+        <v>4</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="5">
+        <v>5</v>
+      </c>
+      <c r="J22" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="7:10">
+      <c r="G23" s="5"/>
+      <c r="H23" s="7">
+        <v>2</v>
+      </c>
+      <c r="I23" s="5">
+        <v>5</v>
+      </c>
+      <c r="J23" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="7:10">
+      <c r="G24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="6">
+        <v>15</v>
+      </c>
+      <c r="J24" s="10">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>